--- a/tools/gfy-admin-template.xlsx
+++ b/tools/gfy-admin-template.xlsx
@@ -640,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Before every send round: export Contacts as CSV and run: npm run presend -- &lt;path outside the repo&gt;</t>
+          <t>Before every send round: export Contacts as CSV (somewhere OUTSIDE the repo) and run: npm run presend -- &lt;that .csv&gt; --vault-url &lt;this sheet's URL&gt;</t>
         </is>
       </c>
     </row>
